--- a/class_diagram/service/manager/成績管理sys_クラス図_service_manager.xlsx
+++ b/class_diagram/service/manager/成績管理sys_クラス図_service_manager.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\class_diagram\service\manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{CB110E73-D601-408B-AFCE-4F5FC9A78A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B7B3EDD-9F8F-457C-8B32-2D2AB317D3DC}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{CB110E73-D601-408B-AFCE-4F5FC9A78A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2304AFB-B7C8-4F4A-B2A9-6D583F4FAB74}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ManagerService" sheetId="3" r:id="rId1"/>
     <sheet name="SubjectService" sheetId="4" r:id="rId2"/>
     <sheet name="MajorService" sheetId="2" r:id="rId3"/>
+    <sheet name="ClassService" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -2256,6 +2257,176 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="四角形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8FACB16-3101-4B7B-8BBA-79625BC5C2E7}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{96E8380A-DEB0-4B22-A05D-A80B00C81033}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6943725" y="1943100"/>
+          <a:ext cx="5695950" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>managersRepository : ManagersRepository</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3977,6 +4148,2058 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t> : DozerBeanMapper</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="四角形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61988B41-3997-4D78-BF62-EC3430D8099E}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{A5F7113C-616A-4865-9774-F76922E5294A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7105650" y="2343150"/>
+          <a:ext cx="5695950" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>managersRepository : ManagersRepository</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="角丸四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2315C3B-9618-45D5-9622-63A72D3B8A3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="1009650"/>
+          <a:ext cx="14801850" cy="6734175"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="90000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr spcFirstLastPara="0" vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="3600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ClassService</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="四角形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72A0748A-906C-4FE2-ABF7-8D136BA67996}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{E2315C3B-9618-45D5-9622-63A72D3B8A3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4095750" y="2990850"/>
+          <a:ext cx="2733675" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getClassById( id  : Integer)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r ClassEntity</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C54B0866-9FC7-41E3-A226-46B444A11DF0}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{72A0748A-906C-4FE2-ABF7-8D136BA67996}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7058025" y="2990850"/>
+          <a:ext cx="2733675" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getClasses()</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r List&lt;ClassEntity&gt;</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>476250</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CE251E8-D8A0-4A64-9D92-99519B361B33}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{C54B0866-9FC7-41E3-A226-46B444A11DF0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1162050" y="3619500"/>
+          <a:ext cx="5838825" cy="1000125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>registerClass( form : ClassRegisterForm, managerId : Integer, majorId : Integer )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r ClassEntity</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{015BDD69-89FC-42AA-89D8-536FCE1B30E9}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2CE251E8-D8A0-4A64-9D92-99519B361B33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7162800" y="3648075"/>
+          <a:ext cx="7562850" cy="838200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>setClass( id : Integer, updates : Map&lt;String, String&gt;, managerId : Integer, majorId : Integer)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r Major</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D56507CF-9685-4426-AE67-044E90B9AA1C}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{015BDD69-89FC-42AA-89D8-536FCE1B30E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1114425" y="5095875"/>
+          <a:ext cx="5838825" cy="723900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>deleteClass( id :   Integer)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96DC0904-16F9-46E2-B0E5-D53B8972A651}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D56507CF-9685-4426-AE67-044E90B9AA1C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1152525" y="2438400"/>
+          <a:ext cx="2733675" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>repository : ClassesRepository</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="四角形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53BB971B-3035-41A8-B5F3-1E1C75854EBE}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{96DC0904-16F9-46E2-B0E5-D53B8972A651}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10287000" y="2943225"/>
+          <a:ext cx="3295650" cy="876300"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getMajorByName( name : String )</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r Major</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="四角形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2AB6B823-1B80-4FAC-803B-968478DFEE20}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{53BB971B-3035-41A8-B5F3-1E1C75854EBE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3971925" y="2438400"/>
+          <a:ext cx="2733675" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>mapper</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t> : DozerBeanMapper</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="四角形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B28C69E4-0F3C-4472-AEA5-B2130C50AC33}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{2AB6B823-1B80-4FAC-803B-968478DFEE20}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7239000" y="1666875"/>
+          <a:ext cx="5695950" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>managersRepository : ManagersRepository</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="四角形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09A5CC11-13B8-4BF3-9D15-23B746372F34}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{B28C69E4-0F3C-4472-AEA5-B2130C50AC33}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7229475" y="1152525"/>
+          <a:ext cx="5695950" cy="428625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>majorsRepository : MajorsRepository</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -4333,4 +6556,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FFE0C6-BAEA-46AB-980B-ED932530F560}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/class_diagram/service/manager/成績管理sys_クラス図_service_manager.xlsx
+++ b/class_diagram/service/manager/成績管理sys_クラス図_service_manager.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\class_diagram\service\manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{CB110E73-D601-408B-AFCE-4F5FC9A78A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2304AFB-B7C8-4F4A-B2A9-6D583F4FAB74}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{CB110E73-D601-408B-AFCE-4F5FC9A78A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E18180F-4DDB-484A-81AF-8AA5754A8120}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ManagerService" sheetId="3" r:id="rId1"/>
@@ -4332,15 +4332,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4355,7 +4355,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685800" y="1009650"/>
+          <a:off x="695325" y="1104900"/>
           <a:ext cx="14801850" cy="6734175"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -4409,16 +4409,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4436,8 +4436,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4095750" y="2990850"/>
-          <a:ext cx="2733675" cy="876300"/>
+          <a:off x="942975" y="2590800"/>
+          <a:ext cx="2733675" cy="723900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4594,16 +4594,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4621,8 +4621,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7058025" y="2990850"/>
-          <a:ext cx="2733675" cy="876300"/>
+          <a:off x="8401050" y="2505075"/>
+          <a:ext cx="2733675" cy="723900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5504,14 +5504,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
@@ -5531,8 +5531,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10287000" y="2943225"/>
-          <a:ext cx="3295650" cy="876300"/>
+          <a:off x="11534775" y="2486025"/>
+          <a:ext cx="3295650" cy="723900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6200,6 +6200,191 @@
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>majorsRepository : MajorsRepository</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1C3704D-EECA-4390-BF8E-8DC3EE63FC37}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{09A5CC11-13B8-4BF3-9D15-23B746372F34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3800475" y="2590800"/>
+          <a:ext cx="3990975" cy="723900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="t" anchorCtr="0" forceAA="0" compatLnSpc="1">
+          <a:prstTxWarp prst="textNoShape">
+            <a:avLst/>
+          </a:prstTxWarp>
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle>
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>getClassesByStartYear(  startYear :   Integer)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" indent="0" algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>-r List&lt;ClassEntity&gt;</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>

--- a/class_diagram/service/manager/成績管理sys_クラス図_service_manager.xlsx
+++ b/class_diagram/service/manager/成績管理sys_クラス図_service_manager.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29622"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java_fri_sys\seiseki_manage_sys\class_diagram\service\manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{CB110E73-D601-408B-AFCE-4F5FC9A78A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E18180F-4DDB-484A-81AF-8AA5754A8120}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{CB110E73-D601-408B-AFCE-4F5FC9A78A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23B1F349-8EDE-4F5D-8063-95CE8787C2A4}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5128,7 +5128,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>setClass( id : Integer, updates : Map&lt;String, String&gt;, managerId : Integer, majorId : Integer)</a:t>
+            <a:t>setClass( id : Integer, updates : Map&lt;String, String&gt;, managerId : Integer )</a:t>
           </a:r>
         </a:p>
         <a:p>
